--- a/docs/oc-mensuales/endoprotesis-ortopedia-y-trauma/may-2026.xlsx
+++ b/docs/oc-mensuales/endoprotesis-ortopedia-y-trauma/may-2026.xlsx
@@ -569,7 +569,7 @@
         </is>
       </c>
       <c r="M2" s="2" t="n">
-        <v>6331.55</v>
+        <v>6293.61</v>
       </c>
     </row>
     <row r="3">
@@ -630,7 +630,7 @@
         </is>
       </c>
       <c r="M3" s="2" t="n">
-        <v>77972.47</v>
+        <v>76912.39</v>
       </c>
     </row>
     <row r="4">
@@ -691,7 +691,7 @@
         </is>
       </c>
       <c r="M4" s="2" t="n">
-        <v>7722.58</v>
+        <v>7764.17</v>
       </c>
     </row>
     <row r="5">
@@ -752,7 +752,7 @@
         </is>
       </c>
       <c r="M5" s="2" t="n">
-        <v>5170.24</v>
+        <v>5228.06</v>
       </c>
     </row>
     <row r="6">
@@ -813,7 +813,7 @@
         </is>
       </c>
       <c r="M6" s="2" t="n">
-        <v>2463.27</v>
+        <v>2490.82</v>
       </c>
     </row>
     <row r="7">
@@ -874,7 +874,7 @@
         </is>
       </c>
       <c r="M7" s="2" t="n">
-        <v>28441.03</v>
+        <v>28759.1</v>
       </c>
     </row>
     <row r="8">
@@ -935,7 +935,7 @@
         </is>
       </c>
       <c r="M8" s="2" t="n">
-        <v>5727.51</v>
+        <v>5770.89</v>
       </c>
     </row>
     <row r="9">
@@ -996,7 +996,7 @@
         </is>
       </c>
       <c r="M9" s="2" t="n">
-        <v>4604.81</v>
+        <v>4622.26</v>
       </c>
     </row>
     <row r="10">
@@ -1057,7 +1057,7 @@
         </is>
       </c>
       <c r="M10" s="2" t="n">
-        <v>7276.48</v>
+        <v>7304.05</v>
       </c>
     </row>
     <row r="11">
@@ -1118,7 +1118,7 @@
         </is>
       </c>
       <c r="M11" s="2" t="n">
-        <v>7516.73</v>
+        <v>7497.75</v>
       </c>
     </row>
     <row r="12">
@@ -1179,7 +1179,7 @@
         </is>
       </c>
       <c r="M12" s="2" t="n">
-        <v>5053.04</v>
+        <v>5040.29</v>
       </c>
     </row>
     <row r="13">
@@ -1240,7 +1240,7 @@
         </is>
       </c>
       <c r="M13" s="2" t="n">
-        <v>28423.04</v>
+        <v>28351.28</v>
       </c>
     </row>
     <row r="14">
@@ -1301,7 +1301,7 @@
         </is>
       </c>
       <c r="M14" s="2" t="n">
-        <v>15161.52</v>
+        <v>15123.24</v>
       </c>
     </row>
     <row r="15">
@@ -1362,7 +1362,7 @@
         </is>
       </c>
       <c r="M15" s="2" t="n">
-        <v>6778.31</v>
+        <v>6761.2</v>
       </c>
     </row>
     <row r="16">
@@ -1423,7 +1423,7 @@
         </is>
       </c>
       <c r="M16" s="2" t="n">
-        <v>33708.48</v>
+        <v>33623.37</v>
       </c>
     </row>
     <row r="17">
@@ -1484,7 +1484,7 @@
         </is>
       </c>
       <c r="M17" s="2" t="n">
-        <v>56594.6</v>
+        <v>56451.71</v>
       </c>
     </row>
     <row r="18">
@@ -1545,7 +1545,7 @@
         </is>
       </c>
       <c r="M18" s="2" t="n">
-        <v>36896.08</v>
+        <v>37246.62</v>
       </c>
     </row>
     <row r="19">
@@ -1606,7 +1606,7 @@
         </is>
       </c>
       <c r="M19" s="2" t="n">
-        <v>5209.15</v>
+        <v>5247.96</v>
       </c>
     </row>
     <row r="20">
@@ -1667,7 +1667,7 @@
         </is>
       </c>
       <c r="M20" s="2" t="n">
-        <v>3231.4</v>
+        <v>3199.17</v>
       </c>
     </row>
     <row r="21">
@@ -1728,7 +1728,7 @@
         </is>
       </c>
       <c r="M21" s="2" t="n">
-        <v>2852.49</v>
+        <v>2824.04</v>
       </c>
     </row>
     <row r="22">
@@ -1789,7 +1789,7 @@
         </is>
       </c>
       <c r="M22" s="2" t="n">
-        <v>6331.55</v>
+        <v>6268.41</v>
       </c>
     </row>
     <row r="23">
@@ -1850,7 +1850,7 @@
         </is>
       </c>
       <c r="M23" s="2" t="n">
-        <v>3123.49</v>
+        <v>3116.4</v>
       </c>
     </row>
     <row r="24">
@@ -1911,7 +1911,7 @@
         </is>
       </c>
       <c r="M24" s="2" t="n">
-        <v>77321.11</v>
+        <v>77145.61</v>
       </c>
     </row>
     <row r="25">
@@ -1972,7 +1972,7 @@
         </is>
       </c>
       <c r="M25" s="2" t="n">
-        <v>2463.27</v>
+        <v>2457.68</v>
       </c>
     </row>
     <row r="26">
@@ -2033,7 +2033,7 @@
         </is>
       </c>
       <c r="M26" s="2" t="n">
-        <v>6363.37</v>
+        <v>6347.65</v>
       </c>
     </row>
     <row r="27">
@@ -2094,7 +2094,7 @@
         </is>
       </c>
       <c r="M27" s="2" t="n">
-        <v>3606.63</v>
+        <v>3597.72</v>
       </c>
     </row>
     <row r="28">
@@ -2155,7 +2155,7 @@
         </is>
       </c>
       <c r="M28" s="2" t="n">
-        <v>3606.63</v>
+        <v>3597.72</v>
       </c>
     </row>
     <row r="29">
@@ -2216,7 +2216,7 @@
         </is>
       </c>
       <c r="M29" s="2" t="n">
-        <v>3606.63</v>
+        <v>3597.72</v>
       </c>
     </row>
     <row r="30">
@@ -2277,7 +2277,7 @@
         </is>
       </c>
       <c r="M30" s="2" t="n">
-        <v>3606.63</v>
+        <v>3597.72</v>
       </c>
     </row>
     <row r="31">
@@ -2338,7 +2338,7 @@
         </is>
       </c>
       <c r="M31" s="2" t="n">
-        <v>3606.63</v>
+        <v>3597.72</v>
       </c>
     </row>
     <row r="32">
@@ -2399,7 +2399,7 @@
         </is>
       </c>
       <c r="M32" s="2" t="n">
-        <v>7213.25</v>
+        <v>7195.44</v>
       </c>
     </row>
     <row r="33">
@@ -2460,7 +2460,7 @@
         </is>
       </c>
       <c r="M33" s="2" t="n">
-        <v>3130.78</v>
+        <v>3123.05</v>
       </c>
     </row>
     <row r="34">
@@ -2521,7 +2521,7 @@
         </is>
       </c>
       <c r="M34" s="2" t="n">
-        <v>2423.82</v>
+        <v>2417.83</v>
       </c>
     </row>
     <row r="35">
@@ -2582,7 +2582,7 @@
         </is>
       </c>
       <c r="M35" s="2" t="n">
-        <v>75767.67999999999</v>
+        <v>76139.87</v>
       </c>
     </row>
     <row r="36">
@@ -2643,7 +2643,7 @@
         </is>
       </c>
       <c r="M36" s="2" t="n">
-        <v>10445.75</v>
+        <v>10497.06</v>
       </c>
     </row>
     <row r="37">
@@ -2704,7 +2704,7 @@
         </is>
       </c>
       <c r="M37" s="2" t="n">
-        <v>3606.63</v>
+        <v>3624.34</v>
       </c>
     </row>
     <row r="38">
@@ -2765,7 +2765,7 @@
         </is>
       </c>
       <c r="M38" s="2" t="n">
-        <v>3635.44</v>
+        <v>3653.3</v>
       </c>
     </row>
     <row r="39">
@@ -2826,7 +2826,7 @@
         </is>
       </c>
       <c r="M39" s="2" t="n">
-        <v>4319.14</v>
+        <v>4333.46</v>
       </c>
     </row>
     <row r="40">
@@ -2887,7 +2887,7 @@
         </is>
       </c>
       <c r="M40" s="2" t="n">
-        <v>24002.62</v>
+        <v>24082.25</v>
       </c>
     </row>
     <row r="41">
@@ -2948,7 +2948,7 @@
         </is>
       </c>
       <c r="M41" s="2" t="n">
-        <v>2770.05</v>
+        <v>2778.87</v>
       </c>
     </row>
     <row r="42">
@@ -3009,7 +3009,7 @@
         </is>
       </c>
       <c r="M42" s="2" t="n">
-        <v>46850.45</v>
+        <v>46999.57</v>
       </c>
     </row>
     <row r="43">
@@ -3070,7 +3070,7 @@
         </is>
       </c>
       <c r="M43" s="2" t="n">
-        <v>36227.15</v>
+        <v>36342.45</v>
       </c>
     </row>
     <row r="44">
@@ -3131,7 +3131,7 @@
         </is>
       </c>
       <c r="M44" s="2" t="n">
-        <v>26544.93</v>
+        <v>26629.42</v>
       </c>
     </row>
     <row r="45">
@@ -3192,7 +3192,7 @@
         </is>
       </c>
       <c r="M45" s="2" t="n">
-        <v>7242.12</v>
+        <v>7280.63</v>
       </c>
     </row>
     <row r="46">
@@ -3253,7 +3253,7 @@
         </is>
       </c>
       <c r="M46" s="2" t="n">
-        <v>2673.58</v>
+        <v>2687.79</v>
       </c>
     </row>
   </sheetData>

--- a/docs/oc-mensuales/endoprotesis-ortopedia-y-trauma/may-2026.xlsx
+++ b/docs/oc-mensuales/endoprotesis-ortopedia-y-trauma/may-2026.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="OC may-2026" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="OC may-2026" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -610,7 +610,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -793,7 +793,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1525,7 +1525,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -1952,7 +1952,7 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">

--- a/docs/oc-mensuales/endoprotesis-ortopedia-y-trauma/may-2026.xlsx
+++ b/docs/oc-mensuales/endoprotesis-ortopedia-y-trauma/may-2026.xlsx
@@ -615,7 +615,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>GLOBALMED SPA</t>
+          <t>GLOBALMED SpA</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -676,7 +676,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>HOSPITALIA Productos Medicos Ltda</t>
+          <t>HOSPITALIA PRODUCTOS MEDICOS LTDA</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -737,7 +737,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>HOSPITALIA Productos Medicos Ltda</t>
+          <t>HOSPITALIA PRODUCTOS MEDICOS LTDA</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -971,7 +971,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>HOSPITAL CLINICO DE LA FUERZA AEREA GRAL DR RAUL YAZIGI JAUREGUI</t>
+          <t>FUERZA AEREA DE CHILE COMANDO LOGISTICO</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1093,7 +1093,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Carabineros de Chile - Hospital de Carabineros</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1530,7 +1530,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>GLOBALMED SPA</t>
+          <t>GLOBALMED SpA</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -1713,7 +1713,7 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>HOSPITALIA Productos Medicos Ltda</t>
+          <t>HOSPITALIA PRODUCTOS MEDICOS LTDA</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -1764,7 +1764,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE SALUD HOSPITAL CARLOS VAN BUR</t>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL CARLOS VAN BUREN</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -2008,7 +2008,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>EJERCITO DE CHILE HOSPITAL MILITAR DE SANTIAGO</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -2435,7 +2435,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Servicio de Salud Coquimbo Hospital de Ovalle</t>
+          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL DE O</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -2445,7 +2445,7 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>HOSPITALIA Productos Medicos Ltda</t>
+          <t>HOSPITALIA PRODUCTOS MEDICOS LTDA</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
@@ -2618,7 +2618,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>HOSPITAL CLINICO DE LA FUERZA AEREA GRAL DR RAUL YAZIGI JAUREGUI</t>
+          <t>FUERZA AEREA DE CHILE COMANDO LOGISTICO</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -2872,7 +2872,7 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>HOSPITALIA Productos Medicos Ltda</t>
+          <t>HOSPITALIA PRODUCTOS MEDICOS LTDA</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
@@ -2913,7 +2913,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -2933,7 +2933,7 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>HOSPITALIA Productos Medicos Ltda</t>
+          <t>HOSPITALIA PRODUCTOS MEDICOS LTDA</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
@@ -3106,7 +3106,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>HOSPITAL NAVAL ALMIRANTE NEF</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -3228,7 +3228,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>EJERCITO DE CHILE HOSPITAL MILITAR DE SANTIAGO</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">

--- a/docs/oc-mensuales/endoprotesis-ortopedia-y-trauma/may-2026.xlsx
+++ b/docs/oc-mensuales/endoprotesis-ortopedia-y-trauma/may-2026.xlsx
@@ -684,7 +684,11 @@
           <t>78.233.420-4</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L4" t="inlineStr">
         <is>
           <t>USD</t>
@@ -745,7 +749,11 @@
           <t>78.233.420-4</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L5" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1660,7 +1668,11 @@
           <t>79.744.580-0</t>
         </is>
       </c>
-      <c r="K20" t="inlineStr"/>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L20" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1721,7 +1733,11 @@
           <t>78.233.420-4</t>
         </is>
       </c>
-      <c r="K21" t="inlineStr"/>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L21" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2453,7 +2469,11 @@
           <t>78.233.420-4</t>
         </is>
       </c>
-      <c r="K33" t="inlineStr"/>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L33" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2575,7 +2595,11 @@
           <t>78.874.470-6</t>
         </is>
       </c>
-      <c r="K35" t="inlineStr"/>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L35" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2880,7 +2904,11 @@
           <t>78.233.420-4</t>
         </is>
       </c>
-      <c r="K40" t="inlineStr"/>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L40" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2941,7 +2969,11 @@
           <t>78.233.420-4</t>
         </is>
       </c>
-      <c r="K41" t="inlineStr"/>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L41" t="inlineStr">
         <is>
           <t>USD</t>

--- a/docs/oc-mensuales/endoprotesis-ortopedia-y-trauma/may-2026.xlsx
+++ b/docs/oc-mensuales/endoprotesis-ortopedia-y-trauma/may-2026.xlsx
@@ -562,7 +562,11 @@
           <t>93.745.000-1</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr"/>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L2" t="inlineStr">
         <is>
           <t>USD</t>
@@ -875,7 +879,11 @@
           <t>93.745.000-1</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr"/>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L7" t="inlineStr">
         <is>
           <t>USD</t>
@@ -936,7 +944,11 @@
           <t>93.745.000-1</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr"/>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L8" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1180,7 +1192,11 @@
           <t>93.745.000-1</t>
         </is>
       </c>
-      <c r="K12" t="inlineStr"/>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L12" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1241,7 +1257,11 @@
           <t>93.745.000-1</t>
         </is>
       </c>
-      <c r="K13" t="inlineStr"/>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L13" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1302,7 +1322,11 @@
           <t>93.745.000-1</t>
         </is>
       </c>
-      <c r="K14" t="inlineStr"/>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L14" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1363,7 +1387,11 @@
           <t>93.745.000-1</t>
         </is>
       </c>
-      <c r="K15" t="inlineStr"/>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L15" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1424,7 +1452,11 @@
           <t>93.745.000-1</t>
         </is>
       </c>
-      <c r="K16" t="inlineStr"/>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L16" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1485,7 +1517,11 @@
           <t>93.745.000-1</t>
         </is>
       </c>
-      <c r="K17" t="inlineStr"/>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L17" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1798,7 +1834,11 @@
           <t>93.745.000-1</t>
         </is>
       </c>
-      <c r="K22" t="inlineStr"/>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L22" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1859,7 +1899,11 @@
           <t>93.745.000-1</t>
         </is>
       </c>
-      <c r="K23" t="inlineStr"/>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L23" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2042,7 +2086,11 @@
           <t>93.745.000-1</t>
         </is>
       </c>
-      <c r="K26" t="inlineStr"/>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L26" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2843,7 +2891,11 @@
           <t>93.745.000-1</t>
         </is>
       </c>
-      <c r="K39" t="inlineStr"/>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L39" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3156,7 +3208,11 @@
           <t>93.745.000-1</t>
         </is>
       </c>
-      <c r="K44" t="inlineStr"/>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L44" t="inlineStr">
         <is>
           <t>USD</t>

--- a/docs/oc-mensuales/endoprotesis-ortopedia-y-trauma/may-2026.xlsx
+++ b/docs/oc-mensuales/endoprotesis-ortopedia-y-trauma/may-2026.xlsx
@@ -851,7 +851,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -1936,7 +1936,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -3180,7 +3180,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
